--- a/MainTop/02.09.2026 имена СТ/Санкт_print_sorted.xlsx
+++ b/MainTop/02.09.2026 имена СТ/Санкт_print_sorted.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\02.09.2026 имена СТ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\02.09.2026 имена СТ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6BE806-4E89-417C-B171-4C8DD49305FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D20C7B4-240A-4CC0-A7BC-8B06FC85B2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -581,7 +581,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -600,6 +600,24 @@
         <bgColor rgb="FF99CCFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF99CCFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -613,10 +631,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -964,13 +985,13 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="3">
         <v>78</v>
       </c>
       <c r="D2" s="1">
@@ -1002,13 +1023,13 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="3">
         <v>34</v>
       </c>
       <c r="D3" s="1">
@@ -1040,13 +1061,13 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="3">
         <v>30</v>
       </c>
       <c r="D4" s="1">
@@ -1078,13 +1099,13 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="3">
         <v>22</v>
       </c>
       <c r="D5" s="1">
@@ -1116,13 +1137,13 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="3">
         <v>20</v>
       </c>
       <c r="D6" s="1">
@@ -1154,13 +1175,13 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="3">
         <v>20</v>
       </c>
       <c r="D7" s="1">
@@ -1192,13 +1213,13 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="3">
         <v>19</v>
       </c>
       <c r="D8" s="1">
@@ -1230,13 +1251,13 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="3">
         <v>18</v>
       </c>
       <c r="D9" s="1">
@@ -1268,13 +1289,13 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="3">
         <v>18</v>
       </c>
       <c r="D10" s="1">
@@ -1306,13 +1327,13 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="3">
         <v>18</v>
       </c>
       <c r="D11" s="1">
@@ -1344,13 +1365,13 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="3">
         <v>18</v>
       </c>
       <c r="D12" s="1">
@@ -1382,13 +1403,13 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="3">
         <v>17</v>
       </c>
       <c r="D13" s="1">
@@ -1420,13 +1441,13 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="3">
         <v>17</v>
       </c>
       <c r="D14" s="1">
@@ -1458,13 +1479,13 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="4">
         <v>17</v>
       </c>
       <c r="D15" s="1">
@@ -1496,13 +1517,13 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="4">
         <v>16</v>
       </c>
       <c r="D16" s="1">
@@ -1534,13 +1555,13 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="4">
         <v>16</v>
       </c>
       <c r="D17" s="1">
@@ -1572,13 +1593,13 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="4">
         <v>15</v>
       </c>
       <c r="D18" s="1">
@@ -1610,13 +1631,13 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="4">
         <v>15</v>
       </c>
       <c r="D19" s="1">
@@ -1648,13 +1669,13 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="4">
         <v>15</v>
       </c>
       <c r="D20" s="1">
@@ -1686,13 +1707,13 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="4">
         <v>14</v>
       </c>
       <c r="D21" s="1">
@@ -1724,13 +1745,13 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="4">
         <v>13</v>
       </c>
       <c r="D22" s="1">
@@ -1762,13 +1783,13 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="4">
         <v>13</v>
       </c>
       <c r="D23" s="1">
@@ -1800,13 +1821,13 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="4">
         <v>13</v>
       </c>
       <c r="D24" s="1">
@@ -1838,13 +1859,13 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="4">
         <v>12</v>
       </c>
       <c r="D25" s="1">
@@ -1876,13 +1897,13 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="4">
         <v>12</v>
       </c>
       <c r="D26" s="1">
@@ -1914,13 +1935,13 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="4">
         <v>12</v>
       </c>
       <c r="D27" s="1">
@@ -1952,13 +1973,13 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="4">
         <v>12</v>
       </c>
       <c r="D28" s="1">
@@ -1990,13 +2011,13 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="4">
         <v>12</v>
       </c>
       <c r="D29" s="1">
@@ -2028,13 +2049,13 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="4">
         <v>11</v>
       </c>
       <c r="D30" s="1">
@@ -2066,13 +2087,13 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="4">
         <v>11</v>
       </c>
       <c r="D31" s="1">
@@ -2104,13 +2125,13 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="4">
         <v>11</v>
       </c>
       <c r="D32" s="1">
@@ -2142,13 +2163,13 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="4">
         <v>10</v>
       </c>
       <c r="D33" s="1">
@@ -2180,13 +2201,13 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="4">
         <v>10</v>
       </c>
       <c r="D34" s="1">
@@ -2218,13 +2239,13 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="4">
         <v>10</v>
       </c>
       <c r="D35" s="1">
@@ -2256,13 +2277,13 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="5">
         <v>10</v>
       </c>
       <c r="D36" s="2">
@@ -2294,13 +2315,13 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="5">
         <v>10</v>
       </c>
       <c r="D37" s="2">
@@ -2332,13 +2353,13 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="5">
         <v>10</v>
       </c>
       <c r="D38" s="2">
@@ -2370,13 +2391,13 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="5">
         <v>9</v>
       </c>
       <c r="D39" s="2">
@@ -2408,13 +2429,13 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="5">
         <v>9</v>
       </c>
       <c r="D40" s="2">
